--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_105_R11.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_105_R11.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.942399999999999</v>
+        <v>9.1447</v>
       </c>
       <c r="E2" t="n">
-        <v>6.9374</v>
+        <v>7.1733</v>
       </c>
       <c r="F2" t="n">
-        <v>2.005</v>
+        <v>1.9714</v>
       </c>
       <c r="G2" t="n">
         <v>4.3595</v>
@@ -610,13 +610,13 @@
         <v>2.3195</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1191</v>
+        <v>0.3213</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.1098</v>
+        <v>0.1261</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2289</v>
+        <v>0.1953</v>
       </c>
       <c r="V2" t="n">
         <v>2.1444</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>N. KALINIC</t>
+          <t>J. BUTLER</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.6672</v>
+        <v>3.5973</v>
       </c>
       <c r="E3" t="n">
-        <v>2.9502</v>
+        <v>4.4845</v>
       </c>
       <c r="F3" t="n">
-        <v>0.717</v>
+        <v>-0.8871</v>
       </c>
       <c r="G3" t="n">
-        <v>2.5477</v>
+        <v>4.1365</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.611</v>
+        <v>0.63</v>
       </c>
       <c r="I3" t="n">
-        <v>3.1587</v>
+        <v>3.5065</v>
       </c>
       <c r="J3" t="n">
-        <v>3.8815</v>
+        <v>4.3514</v>
       </c>
       <c r="K3" t="n">
-        <v>0.7163</v>
+        <v>1.0524</v>
       </c>
       <c r="L3" t="n">
-        <v>3.1652</v>
+        <v>3.299</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.3338</v>
+        <v>-0.2148</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.3273</v>
+        <v>-0.4223</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.0065</v>
+        <v>0.2075</v>
       </c>
       <c r="P3" t="n">
-        <v>1.3917</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R3" t="n">
-        <v>2.5515</v>
+        <v>1.1598</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8</v>
+        <v>0.3912</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2284</v>
+        <v>0.0788</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5715</v>
+        <v>0.3123</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.0722</v>
+        <v>-0.9304</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.214</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.0722</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>U. PLAVSIC</t>
+          <t>N. KALINIC</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.2705</v>
+        <v>3.3379</v>
       </c>
       <c r="E4" t="n">
-        <v>1.9773</v>
+        <v>2.789</v>
       </c>
       <c r="F4" t="n">
-        <v>1.2932</v>
+        <v>0.549</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.7648</v>
+        <v>2.5477</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.0793</v>
+        <v>-0.611</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3145</v>
+        <v>3.1587</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2256</v>
+        <v>3.8815</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.5105</v>
+        <v>0.7163</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7361</v>
+        <v>3.1652</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.9903999999999999</v>
+        <v>-1.3338</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.5688</v>
+        <v>-1.3273</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.4216</v>
+        <v>-0.0065</v>
       </c>
       <c r="P4" t="n">
-        <v>0.9278</v>
+        <v>1.3917</v>
       </c>
       <c r="Q4" t="n">
+        <v>-1.1598</v>
+      </c>
+      <c r="R4" t="n">
+        <v>2.5515</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.4707</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.0672</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.4035</v>
+      </c>
+      <c r="V4" t="n">
+        <v>-1.0722</v>
+      </c>
+      <c r="W4" t="n">
         <v>0</v>
       </c>
-      <c r="R4" t="n">
-        <v>0.9278</v>
-      </c>
-      <c r="S4" t="n">
-        <v>2.9657</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.3986</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0.5671</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0.1418</v>
-      </c>
-      <c r="W4" t="n">
-        <v>-0.6468</v>
-      </c>
       <c r="X4" t="n">
-        <v>0.7886</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. BUTLER</t>
+          <t>U. PLAVSIC</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.57</v>
+        <v>1.5856</v>
       </c>
       <c r="E5" t="n">
-        <v>3.6588</v>
+        <v>0.326</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.0888</v>
+        <v>1.2596</v>
       </c>
       <c r="G5" t="n">
-        <v>4.1365</v>
+        <v>-0.7648</v>
       </c>
       <c r="H5" t="n">
-        <v>0.63</v>
+        <v>-1.0793</v>
       </c>
       <c r="I5" t="n">
-        <v>3.5065</v>
+        <v>0.3145</v>
       </c>
       <c r="J5" t="n">
-        <v>4.3514</v>
+        <v>0.2256</v>
       </c>
       <c r="K5" t="n">
-        <v>1.0524</v>
+        <v>-0.5105</v>
       </c>
       <c r="L5" t="n">
-        <v>3.299</v>
+        <v>0.7361</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.2148</v>
+        <v>-0.9903999999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.4223</v>
+        <v>-0.5688</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2075</v>
+        <v>-0.4216</v>
       </c>
       <c r="P5" t="n">
+        <v>0.9278</v>
+      </c>
+      <c r="Q5" t="n">
         <v>0</v>
       </c>
-      <c r="Q5" t="n">
-        <v>-1.1598</v>
-      </c>
       <c r="R5" t="n">
-        <v>1.1598</v>
+        <v>0.9278</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.6361</v>
+        <v>1.2808</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.7468</v>
+        <v>0.7472</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1107</v>
+        <v>0.5335</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.9304</v>
+        <v>0.1418</v>
       </c>
       <c r="W5" t="n">
-        <v>1.214</v>
+        <v>-0.6468</v>
       </c>
       <c r="X5" t="n">
-        <v>-2.1444</v>
+        <v>0.7886</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.4239</v>
+        <v>1.1954</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.6348</v>
+        <v>-0.796</v>
       </c>
       <c r="F6" t="n">
-        <v>2.0586</v>
+        <v>1.9914</v>
       </c>
       <c r="G6" t="n">
         <v>3.4144</v>
@@ -922,13 +922,13 @@
         <v>3.2473</v>
       </c>
       <c r="S6" t="n">
-        <v>0.4191</v>
+        <v>0.1907</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1537</v>
+        <v>-0.0075</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2653</v>
+        <v>0.1981</v>
       </c>
       <c r="V6" t="n">
         <v>0.1418</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.3106</v>
+        <v>0.3374</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.2346</v>
+        <v>-1.4522</v>
       </c>
       <c r="F7" t="n">
-        <v>1.924</v>
+        <v>1.7896</v>
       </c>
       <c r="G7" t="n">
         <v>0.1996</v>
@@ -1000,13 +1000,13 @@
         <v>2.7834</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0439</v>
+        <v>0.6919</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3339</v>
+        <v>0.4485</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3778</v>
+        <v>0.2434</v>
       </c>
       <c r="V7" t="n">
         <v>0.1418</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.6322</v>
+        <v>-1.4738</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.6387</v>
+        <v>-1.682</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0065</v>
+        <v>0.2081</v>
       </c>
       <c r="G8" t="n">
         <v>-3.1228</v>
@@ -1078,13 +1078,13 @@
         <v>1.8556</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2232</v>
+        <v>-0.0648</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2592</v>
+        <v>-0.3025</v>
       </c>
       <c r="U8" t="n">
-        <v>0.036</v>
+        <v>0.2377</v>
       </c>
       <c r="V8" t="n">
         <v>-0.1418</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.8536</v>
+        <v>-1.6273</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.0166</v>
+        <v>-0.824</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.8369</v>
+        <v>-0.8033</v>
       </c>
       <c r="G9" t="n">
         <v>-0.9560999999999999</v>
@@ -1156,13 +1156,13 @@
         <v>0.6959</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4336</v>
+        <v>-0.2074</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2987</v>
+        <v>-0.1061</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1349</v>
+        <v>-0.1013</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,10 +1189,10 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.7624</v>
+        <v>-2.4085</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.1415</v>
+        <v>-1.7876</v>
       </c>
       <c r="F10" t="n">
         <v>-0.6209</v>
@@ -1234,10 +1234,10 @@
         <v>1.8556</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6959</v>
+        <v>-0.342</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5975</v>
+        <v>-0.2436</v>
       </c>
       <c r="U10" t="n">
         <v>-0.0984</v>
@@ -1267,16 +1267,16 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>13.3152</v>
+        <v>13.6887</v>
       </c>
       <c r="E11" t="n">
-        <v>7.857500000000002</v>
+        <v>8.231000000000002</v>
       </c>
       <c r="F11" t="n">
-        <v>5.4577</v>
+        <v>5.457800000000001</v>
       </c>
       <c r="G11" t="n">
-        <v>6.6805</v>
+        <v>6.680499999999999</v>
       </c>
       <c r="H11" t="n">
         <v>-8.811499999999999</v>
@@ -1288,7 +1288,7 @@
         <v>16.8702</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.4945999999999997</v>
+        <v>-0.4946000000000002</v>
       </c>
       <c r="L11" t="n">
         <v>17.3649</v>
@@ -1312,16 +1312,16 @@
         <v>17.3964</v>
       </c>
       <c r="S11" t="n">
-        <v>2.359</v>
+        <v>2.7324</v>
       </c>
       <c r="T11" t="n">
-        <v>0.4348000000000002</v>
+        <v>0.8080999999999998</v>
       </c>
       <c r="U11" t="n">
-        <v>1.924</v>
+        <v>1.9241</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.3631999999999999</v>
+        <v>-0.3632</v>
       </c>
       <c r="W11" t="n">
         <v>3.3098</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>1.6372</v>
+        <v>2.345</v>
       </c>
       <c r="E12" t="n">
-        <v>2.5842</v>
+        <v>3.2919</v>
       </c>
       <c r="F12" t="n">
         <v>-0.9469</v>
@@ -1390,10 +1390,10 @@
         <v>1.6237</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.2423</v>
+        <v>-0.5346</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.1202</v>
+        <v>-0.4125</v>
       </c>
       <c r="U12" t="n">
         <v>-0.1221</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>J. BLOSSOMGAME</t>
+          <t>N. MIROTIC</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,64 +1423,64 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.5123</v>
+        <v>0.4921</v>
       </c>
       <c r="E13" t="n">
-        <v>2.1923</v>
+        <v>-0.1728</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.68</v>
+        <v>0.6647999999999999</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.1767</v>
+        <v>0.3169</v>
       </c>
       <c r="H13" t="n">
-        <v>0.0948</v>
+        <v>3.1476</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.2715</v>
+        <v>-2.8307</v>
       </c>
       <c r="J13" t="n">
-        <v>0.8249</v>
+        <v>0.9744</v>
       </c>
       <c r="K13" t="n">
-        <v>0.3599</v>
+        <v>2.4367</v>
       </c>
       <c r="L13" t="n">
-        <v>0.465</v>
+        <v>-1.4623</v>
       </c>
       <c r="M13" t="n">
-        <v>-2.0016</v>
+        <v>-0.6576</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.2651</v>
+        <v>0.7109</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.7365</v>
+        <v>-1.3684</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.232</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.3917</v>
+        <v>-1.1598</v>
       </c>
       <c r="R13" t="n">
         <v>1.1598</v>
       </c>
       <c r="S13" t="n">
-        <v>1.9905</v>
+        <v>0.0334</v>
       </c>
       <c r="T13" t="n">
-        <v>1.6869</v>
+        <v>-0.2711</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3036</v>
+        <v>0.3044</v>
       </c>
       <c r="V13" t="n">
-        <v>0.9304</v>
+        <v>0.1418</v>
       </c>
       <c r="W13" t="n">
-        <v>1.0722</v>
+        <v>0.2836</v>
       </c>
       <c r="X13" t="n">
         <v>-0.1418</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>N. MIROTIC</t>
+          <t>K. HAYES</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6607</v>
+        <v>0.1593</v>
       </c>
       <c r="E14" t="n">
-        <v>0.0631</v>
+        <v>-0.1566</v>
       </c>
       <c r="F14" t="n">
-        <v>0.5976</v>
+        <v>0.3159</v>
       </c>
       <c r="G14" t="n">
-        <v>0.3169</v>
+        <v>0.2706</v>
       </c>
       <c r="H14" t="n">
-        <v>3.1476</v>
+        <v>1.8799</v>
       </c>
       <c r="I14" t="n">
-        <v>-2.8307</v>
+        <v>-1.6094</v>
       </c>
       <c r="J14" t="n">
-        <v>0.9744</v>
+        <v>1.1995</v>
       </c>
       <c r="K14" t="n">
-        <v>2.4367</v>
+        <v>1.1259</v>
       </c>
       <c r="L14" t="n">
-        <v>-1.4623</v>
+        <v>0.0736</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.6576</v>
+        <v>-0.929</v>
       </c>
       <c r="N14" t="n">
-        <v>0.7109</v>
+        <v>0.754</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.3684</v>
+        <v>-1.683</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>-0.232</v>
       </c>
       <c r="Q14" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R14" t="n">
-        <v>1.1598</v>
+        <v>0.9278</v>
       </c>
       <c r="S14" t="n">
-        <v>0.2021</v>
+        <v>0.2625</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.0351</v>
+        <v>-0.1964</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2372</v>
+        <v>0.4589</v>
       </c>
       <c r="V14" t="n">
-        <v>0.1418</v>
+        <v>-0.1418</v>
       </c>
       <c r="W14" t="n">
-        <v>0.2836</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
         <v>-0.1418</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>K. HAYES</t>
+          <t>J. BLOSSOMGAME</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2944</v>
+        <v>-0.0369</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0793</v>
+        <v>1.0128</v>
       </c>
       <c r="F15" t="n">
-        <v>0.2151</v>
+        <v>-1.0497</v>
       </c>
       <c r="G15" t="n">
-        <v>0.2706</v>
+        <v>-1.1767</v>
       </c>
       <c r="H15" t="n">
-        <v>1.8799</v>
+        <v>0.0948</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.6094</v>
+        <v>-1.2715</v>
       </c>
       <c r="J15" t="n">
-        <v>1.1995</v>
+        <v>0.8249</v>
       </c>
       <c r="K15" t="n">
-        <v>1.1259</v>
+        <v>0.3599</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0736</v>
+        <v>0.465</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.929</v>
+        <v>-2.0016</v>
       </c>
       <c r="N15" t="n">
-        <v>0.754</v>
+        <v>-0.2651</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.683</v>
+        <v>-1.7365</v>
       </c>
       <c r="P15" t="n">
         <v>-0.232</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.1598</v>
+        <v>-1.3917</v>
       </c>
       <c r="R15" t="n">
-        <v>0.9278</v>
+        <v>1.1598</v>
       </c>
       <c r="S15" t="n">
-        <v>0.3976</v>
+        <v>0.4413</v>
       </c>
       <c r="T15" t="n">
-        <v>0.0395</v>
+        <v>0.5074</v>
       </c>
       <c r="U15" t="n">
-        <v>0.358</v>
+        <v>-0.06610000000000001</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.1418</v>
+        <v>0.9304</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X15" t="n">
         <v>-0.1418</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.1709</v>
+        <v>-0.4227</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.801</v>
+        <v>-1.683</v>
       </c>
       <c r="F16" t="n">
-        <v>1.6301</v>
+        <v>1.2604</v>
       </c>
       <c r="G16" t="n">
         <v>-1.7666</v>
@@ -1702,13 +1702,13 @@
         <v>0.232</v>
       </c>
       <c r="S16" t="n">
-        <v>0.575</v>
+        <v>0.3233</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2987</v>
+        <v>-0.1808</v>
       </c>
       <c r="U16" t="n">
-        <v>0.8738</v>
+        <v>0.5041</v>
       </c>
       <c r="V16" t="n">
         <v>0.7886</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.7278</v>
+        <v>-0.9808</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.1224</v>
+        <v>-1.4762</v>
       </c>
       <c r="F17" t="n">
-        <v>0.3946</v>
+        <v>0.4954</v>
       </c>
       <c r="G17" t="n">
         <v>-0.7361</v>
@@ -1780,13 +1780,13 @@
         <v>0.6959</v>
       </c>
       <c r="S17" t="n">
-        <v>0.4722</v>
+        <v>0.2192</v>
       </c>
       <c r="T17" t="n">
-        <v>0.4876</v>
+        <v>0.1338</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0154</v>
+        <v>0.0854</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.4549</v>
+        <v>-1.394</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1437</v>
+        <v>0.9694</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.5986</v>
+        <v>-2.3634</v>
       </c>
       <c r="G18" t="n">
         <v>-0.2845</v>
@@ -1858,13 +1858,13 @@
         <v>2.3195</v>
       </c>
       <c r="S18" t="n">
-        <v>-2.2453</v>
+        <v>-1.1844</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.4936</v>
+        <v>-0.668</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.7516</v>
+        <v>-0.5164</v>
       </c>
       <c r="V18" t="n">
         <v>1.4665</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.4399</v>
+        <v>-2.5484</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.6065</v>
+        <v>-1.2526</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.8334</v>
+        <v>-1.2957</v>
       </c>
       <c r="G19" t="n">
         <v>0.4357</v>
@@ -1936,13 +1936,13 @@
         <v>1.3917</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.4813</v>
+        <v>-0.5898</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.8962</v>
+        <v>-0.5423</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5851</v>
+        <v>-0.0474</v>
       </c>
       <c r="V19" t="n">
         <v>-1.4665</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. DIALLO</t>
+          <t>D. THEIS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-5.2858</v>
+        <v>-5.2398</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.2177</v>
+        <v>-2.7728</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.0681</v>
+        <v>-2.467</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.1784</v>
+        <v>-2.1885</v>
       </c>
       <c r="H20" t="n">
-        <v>0.6351</v>
+        <v>-0.1642</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.8135</v>
+        <v>-2.0243</v>
       </c>
       <c r="J20" t="n">
-        <v>1.4667</v>
+        <v>-0.1115</v>
       </c>
       <c r="K20" t="n">
-        <v>0.9649</v>
+        <v>0.4908</v>
       </c>
       <c r="L20" t="n">
-        <v>0.5018</v>
+        <v>-0.6022999999999999</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.6451</v>
+        <v>-2.077</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.3298</v>
+        <v>-0.6551</v>
       </c>
       <c r="O20" t="n">
-        <v>-2.3153</v>
+        <v>-1.422</v>
       </c>
       <c r="P20" t="n">
-        <v>-2.0876</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.7112</v>
+        <v>-2.5515</v>
       </c>
       <c r="R20" t="n">
         <v>1.6237</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.159</v>
+        <v>-0.7677</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1845</v>
+        <v>-0.1098</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0255</v>
+        <v>-0.6578000000000001</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.8608</v>
+        <v>-1.3558</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.7886</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.0722</v>
+        <v>-1.3558</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>D. THEIS</t>
+          <t>A. DIALLO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.3406</v>
+        <v>-5.6891</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.7728</v>
+        <v>-3.2177</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.5678</v>
+        <v>-2.4714</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.1885</v>
+        <v>-1.1784</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.1642</v>
+        <v>0.6351</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.0243</v>
+        <v>-1.8135</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.1115</v>
+        <v>1.4667</v>
       </c>
       <c r="K21" t="n">
-        <v>0.4908</v>
+        <v>0.9649</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.6022999999999999</v>
+        <v>0.5018</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.077</v>
+        <v>-2.6451</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.6551</v>
+        <v>-0.3298</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.422</v>
+        <v>-2.3153</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.9278</v>
+        <v>-2.0876</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.5515</v>
+        <v>-3.7112</v>
       </c>
       <c r="R21" t="n">
         <v>1.6237</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.8685</v>
+        <v>-0.5623</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1098</v>
+        <v>-0.1845</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.7587</v>
+        <v>-0.3778</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.3558</v>
+        <v>-1.8608</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>-0.7886</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.3558</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="22">
@@ -2128,10 +2128,10 @@
         <v>-13.3153</v>
       </c>
       <c r="E22" t="n">
-        <v>-5.4578</v>
+        <v>-5.4576</v>
       </c>
       <c r="F22" t="n">
-        <v>-7.857399999999999</v>
+        <v>-7.857600000000001</v>
       </c>
       <c r="G22" t="n">
         <v>-6.6806</v>
@@ -2149,19 +2149,19 @@
         <v>8.3169</v>
       </c>
       <c r="L22" t="n">
-        <v>1.873000000000001</v>
+        <v>1.873</v>
       </c>
       <c r="M22" t="n">
         <v>-16.8704</v>
       </c>
       <c r="N22" t="n">
-        <v>0.4945999999999997</v>
+        <v>0.4945999999999998</v>
       </c>
       <c r="O22" t="n">
         <v>-17.3649</v>
       </c>
       <c r="P22" t="n">
-        <v>-4.639099999999999</v>
+        <v>-4.6391</v>
       </c>
       <c r="Q22" t="n">
         <v>-17.3965</v>
@@ -2170,13 +2170,13 @@
         <v>12.7576</v>
       </c>
       <c r="S22" t="n">
-        <v>-2.359</v>
+        <v>-2.3591</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.9241</v>
+        <v>-1.9242</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4348</v>
+        <v>-0.4348000000000001</v>
       </c>
       <c r="V22" t="n">
         <v>0.3631999999999997</v>
